--- a/artfynd/A 47631-2025 artfynd.xlsx
+++ b/artfynd/A 47631-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>7071091</v>
       </c>
       <c r="B2" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -730,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>354347.4088125106</v>
+        <v>354347</v>
       </c>
       <c r="R2" t="n">
-        <v>6585407.42962178</v>
+        <v>6585407</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -763,19 +758,9 @@
           <t>2013-07-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-07-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
